--- a/results/corr_groups_2025_12_15-0012_BIEXP_ALS.xlsx
+++ b/results/corr_groups_2025_12_15-0012_BIEXP_ALS.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,12 +442,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[0, 23, 35, 48, 75, 84, 94, 114, 147, 158, 191, 194, 199, 206, 209]</t>
+          <t>[0, 12, 18, 47, 101, 104, 107]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[16, 17, 18, 19, 20, 159, 160, 161, 210, 211, 212, 213, 214, 269, 270, 271, 272, 273, 274, 433, 434, 435, 436, 491, 492, 493, 494, 549, 550, 551, 552, 553, 659, 660, 846, 847, 848, 907, 908, 909, 910, 911, 912, 1092, 1094, 1095, 1113, 1114, 1115, 1167, 1168, 1169, 1170, 1171, 1183, 1184, 1185, 1186]</t>
+          <t>[16, 17, 18, 177, 178, 179, 180, 181, 182, 210, 211, 491, 492, 493, 494, 1092, 1093, 1094, 1113, 1114, 1167, 1168, 1169]</t>
         </is>
       </c>
     </row>
@@ -457,12 +457,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[2, 81, 123, 185]</t>
+          <t>[2, 27, 57, 73]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[27, 473, 474, 723, 724, 725, 1072]</t>
+          <t>[41, 42, 43, 44, 279, 280, 281, 588, 589, 590, 591, 784, 785, 786]</t>
         </is>
       </c>
     </row>
@@ -472,12 +472,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[3, 49, 101, 132]</t>
+          <t>[5, 6, 7, 40]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[41, 42, 43, 44, 45, 279, 280, 281, 282, 588, 589, 590, 591, 592, 593, 783, 784, 785, 786, 787]</t>
+          <t>[84, 86, 87, 113, 114, 419, 420]</t>
         </is>
       </c>
     </row>
@@ -487,12 +487,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[4, 53, 144, 152]</t>
+          <t>[8, 11, 49, 70, 96]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[45, 46, 47, 295, 842, 843, 878]</t>
+          <t>[144, 145, 146, 147, 173, 174, 509, 510, 511, 512, 513, 720, 1025, 1026, 1027, 1028, 1029, 1030]</t>
         </is>
       </c>
     </row>
@@ -502,12 +502,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[5, 161]</t>
+          <t>[9, 14]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[47, 48, 49, 918]</t>
+          <t>[150, 151, 200, 201]</t>
         </is>
       </c>
     </row>
@@ -517,12 +517,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[6, 59]</t>
+          <t>[10, 25, 42, 53, 67, 81, 88, 109]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[51, 335]</t>
+          <t>[159, 160, 161, 269, 270, 271, 434, 435, 549, 550, 551, 657, 658, 659, 847, 848, 907, 908, 909, 910, 1184, 1185]</t>
         </is>
       </c>
     </row>
@@ -532,12 +532,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[8, 10, 14, 71, 72]</t>
+          <t>[15, 51, 58, 64, 71, 74, 79, 85, 90, 98]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[77, 78, 79, 80, 81, 84, 85, 86, 87, 88, 113, 114, 115, 419, 420, 421, 422, 427, 428]</t>
+          <t>[201, 202, 203, 204, 519, 520, 601, 602, 603, 604, 640, 641, 642, 643, 721, 722, 723, 724, 801, 802, 803, 804, 841, 842, 843, 881, 882, 883, 921, 922, 923, 1076, 1077, 1078, 1079]</t>
         </is>
       </c>
     </row>
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[12, 170]</t>
+          <t>[19, 26, 80]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[99, 966, 967]</t>
+          <t>[213, 273, 842]</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[15, 37]</t>
+          <t>[20, 21, 22, 37, 62]</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[114, 222]</t>
+          <t>[231, 232, 233, 234, 235, 237, 240, 404, 405, 406, 407, 622, 623, 624, 625]</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[16, 77, 178]</t>
+          <t>[28, 30, 100]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[133, 445, 446, 1012, 1013]</t>
+          <t>[284, 285, 326, 327, 1090, 1091, 1092, 1093, 1094]</t>
         </is>
       </c>
     </row>
@@ -592,12 +592,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[19, 88, 92, 179]</t>
+          <t>[29, 32, 45, 75, 97, 103, 110]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[144, 145, 146, 147, 509, 510, 511, 512, 513, 524, 525, 526, 527, 1025, 1026, 1027, 1028, 1029]</t>
+          <t>[322, 323, 324, 349, 350, 467, 468, 811, 812, 813, 1071, 1072, 1073, 1107, 1193, 1194]</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[20, 27, 33, 39, 168]</t>
+          <t>[31, 106]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[146, 147, 148, 179, 180, 204, 205, 229, 953, 954, 955, 956]</t>
+          <t>[348, 1153]</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[21, 60, 112, 131, 136, 141, 205]</t>
+          <t>[43, 44, 46]</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[150, 151, 152, 153, 347, 348, 349, 350, 655, 656, 780, 805, 825, 826, 1153, 1154, 1155]</t>
+          <t>[437, 438, 439, 440, 441, 442, 443, 444, 446, 447, 448, 449, 487]</t>
         </is>
       </c>
     </row>
@@ -637,12 +637,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[22, 90, 156]</t>
+          <t>[76, 77, 78, 82]</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[153, 154, 513, 514, 896, 897, 898, 899]</t>
+          <t>[820, 821, 822, 826, 827, 828, 829, 838, 839, 849, 850]</t>
         </is>
       </c>
     </row>
@@ -652,282 +652,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[26, 55, 61, 184]</t>
+          <t>[86, 99, 108]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[177, 178, 179, 180, 181, 182, 183, 322, 323, 324, 325, 349, 350, 351, 1071, 1072, 1073, 1074, 1075]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>[28, 64, 164, 186, 211]</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>[187, 188, 375, 924, 1076, 1077, 1190]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>[29, 30, 44, 119]</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>[190, 191, 196, 197, 243, 244, 702, 703, 704]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>[32, 91, 103, 110, 122, 135, 143, 153, 162, 187]</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>[201, 202, 203, 204, 519, 520, 601, 602, 603, 604, 640, 641, 642, 643, 721, 722, 723, 724, 801, 802, 803, 804, 841, 842, 843, 881, 882, 883, 921, 922, 1076, 1077, 1078, 1079]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>[34, 42, 51, 54, 73, 89, 98, 104, 149, 157]</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>[206, 207, 208, 209, 210, 241, 242, 243, 284, 285, 286, 303, 304, 305, 431, 511, 512, 572, 573, 574, 607, 608, 609, 864, 865, 866, 907, 908, 909]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>[36, 96]</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>[215, 216, 556]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>[41, 69, 78, 106, 137, 198, 212]</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>[231, 232, 233, 234, 235, 236, 237, 238, 239, 240, 241, 404, 405, 406, 407, 466, 467, 468, 469, 621, 622, 623, 624, 625, 626, 811, 812, 813, 814, 815, 1107, 1108, 1109, 1193, 1194, 1195, 1196]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>[43, 50, 97, 102]</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>[243, 244, 280, 281, 562, 590]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>[47, 127, 193]</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>[261, 763, 764, 765, 1094, 1095]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>[56, 68]</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>[326, 327, 328, 404, 405, 406]</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>[63, 67, 79, 116, 124]</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>[358, 359, 360, 361, 378, 379, 380, 467, 468, 469, 681, 682, 683, 727, 728, 729]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>[76, 83]</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>[437, 438, 439, 440, 441, 442, 443, 444, 445, 446, 447, 448, 449, 450, 451, 452, 453, 454, 486, 487, 488, 489]</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>[82, 108]</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>[477, 633]</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>[85, 128]</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>[493, 494, 765, 766]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>[93, 129, 204]</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[539, 771, 1127]</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>[133, 176, 180]</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>[784, 785, 1005, 1006, 1029, 1030, 1031]</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>[139, 140, 142]</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>[820, 821, 822, 823, 825, 826, 827, 828, 829, 830, 831, 838, 839, 840]</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>[154, 189, 208]</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>[885, 886, 887, 888, 1086, 1087, 1088, 1180, 1181, 1182]</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>[166, 195]</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>[944, 945, 1095]</t>
+          <t>[885, 886, 887, 1086, 1087, 1180, 1181]</t>
         </is>
       </c>
     </row>
@@ -942,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -968,12 +698,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[1, 31, 52, 118]</t>
+          <t>[1, 91, 102]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[23, 24, 25, 200, 201, 202, 203, 285, 701]</t>
+          <t>[24, 944, 1096]</t>
         </is>
       </c>
     </row>
@@ -983,12 +713,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[7, 24, 58, 70, 80, 113, 115, 120, 125, 126, 134, 146, 151, 155, 177, 183, 197, 207, 213]</t>
+          <t>[3, 60, 84, 95]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[66, 161, 162, 334, 409, 470, 659, 680, 705, 745, 749, 801, 843, 870, 894, 1010, 1050, 1107, 1172, 1194]</t>
+          <t>[46, 621, 878, 1005]</t>
         </is>
       </c>
     </row>
@@ -998,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[9, 18, 38, 165, 214]</t>
+          <t>[4, 41, 69]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[83, 135, 222, 928, 1197]</t>
+          <t>[78, 428, 692, 693]</t>
         </is>
       </c>
     </row>
@@ -1013,12 +743,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[11, 66, 100]</t>
+          <t>[16, 17, 23, 24, 34, 36, 39, 56, 59, 68, 72, 83, 89]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[96, 377, 582]</t>
+          <t>[206, 207, 209, 241, 261, 359, 378, 379, 405, 573, 607, 608, 681, 682, 763, 864, 865, 909]</t>
         </is>
       </c>
     </row>
@@ -1028,12 +758,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[13, 159]</t>
+          <t>[35, 63]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[99, 910]</t>
+          <t>[377, 623]</t>
         </is>
       </c>
     </row>
@@ -1043,12 +773,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[17, 188]</t>
+          <t>[38, 93, 94]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[134, 1082]</t>
+          <t>[404, 958, 959, 972, 973]</t>
         </is>
       </c>
     </row>
@@ -1058,12 +788,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[25, 121]</t>
+          <t>[48, 55]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[173, 720]</t>
+          <t>[507, 508, 572, 573]</t>
         </is>
       </c>
     </row>
@@ -1073,177 +803,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[40, 62, 105, 130, 138, 175]</t>
+          <t>[66, 87]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[231, 356, 357, 616, 773, 819, 992]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>[45, 74, 190]</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>[259, 433, 1090, 1091, 1092]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>[46, 173]</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>[260, 979]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>[57, 117]</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>[329, 692, 693, 694]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>[65, 174]</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>[376, 377, 984]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>[86, 145]</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>[502, 842]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>[87, 99]</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>[507, 508, 572, 573]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>[95, 150, 160]</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>[551, 552, 553, 867, 911]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>[107, 169, 172]</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>[622, 958, 959, 972, 973, 974]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>[111, 148, 192]</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>[655, 656, 657, 658, 849, 850, 851, 1093]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>[163, 200, 203]</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>[923, 1120, 1121, 1123]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>[196, 210]</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>[1096, 1188]</t>
+          <t>[657, 896]</t>
         </is>
       </c>
     </row>
@@ -1258,7 +823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1275,71 +840,91 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[640]</t>
+          <t>[190]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>167</v>
+        <v>33</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[952]</t>
+          <t>[356]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[972]</t>
+          <t>[513]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>181</v>
+        <v>52</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[1034]</t>
+          <t>[524, 525, 526, 527]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[1035]</t>
+          <t>[551, 552]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>201</v>
+        <v>61</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[1122]</t>
+          <t>[621]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>202</v>
+        <v>65</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[1122]</t>
+          <t>[655, 656]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>92</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>[953]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>105</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[1119, 1120, 1121, 1122, 1123]</t>
         </is>
       </c>
     </row>
@@ -1354,7 +939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1378,6 +963,21 @@
           <t>pixel_area</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>n_events</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>period_s</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>freq_hz</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1389,10 +989,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>103794</v>
+        <v>107038</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9.591666666666667</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.104257167680278</v>
       </c>
     </row>
     <row r="3">
@@ -1408,7 +1017,16 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>18498</v>
+        <v>98657</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12.38333333333333</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.08075370121130553</v>
       </c>
     </row>
     <row r="4">
@@ -1424,7 +1042,16 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>133896</v>
+        <v>27349</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5.583333333333334</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1791044776119403</v>
       </c>
     </row>
     <row r="5">
@@ -1437,10 +1064,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>48776</v>
+        <v>154785</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>11.0125</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.09080590238365495</v>
       </c>
     </row>
     <row r="6">
@@ -1456,7 +1092,16 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>13986</v>
+        <v>19094</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="7">
@@ -1469,10 +1114,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>6549</v>
+        <v>84435</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7.321428571428571</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1365853658536585</v>
       </c>
     </row>
     <row r="8">
@@ -1485,10 +1139,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>79519</v>
+        <v>176453</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4.861111111111112</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2057142857142857</v>
       </c>
     </row>
     <row r="9">
@@ -1501,10 +1164,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>10503</v>
+        <v>21053</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>15.725</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.06359300476947535</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1189,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>8274</v>
+        <v>153431</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.8875</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.2046035805626598</v>
       </c>
     </row>
     <row r="11">
@@ -1536,7 +1217,16 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>17774</v>
+        <v>64390</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.04962779156327544</v>
       </c>
     </row>
     <row r="12">
@@ -1549,10 +1239,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>193096</v>
+        <v>86754</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7.258333333333333</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1377726750861079</v>
       </c>
     </row>
     <row r="13">
@@ -1565,10 +1264,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>43146</v>
+        <v>5838</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.02484472049689441</v>
       </c>
     </row>
     <row r="14">
@@ -1581,10 +1289,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>49898</v>
+        <v>63803</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="15">
@@ -1597,10 +1314,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>32839</v>
+        <v>114110</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.4833333333333333</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.068965517241379</v>
       </c>
     </row>
     <row r="16">
@@ -1613,10 +1339,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>139770</v>
+        <v>34733</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7.375</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.1355932203389831</v>
       </c>
     </row>
     <row r="17">
@@ -1625,14 +1360,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>group 15</t>
+          <t>centroid_group 0</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>16779</v>
+        <v>10518</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.03731343283582089</v>
       </c>
     </row>
     <row r="18">
@@ -1641,14 +1385,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>group 16</t>
+          <t>centroid_group 1</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>45699</v>
+        <v>28735</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="n">
+        <v>15.98333333333333</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.06256517205422314</v>
       </c>
     </row>
     <row r="19">
@@ -1657,14 +1410,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>group 17</t>
+          <t>centroid_group 2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>202676</v>
+        <v>47602</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.06514657980456026</v>
       </c>
     </row>
     <row r="20">
@@ -1673,14 +1435,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>group 18</t>
+          <t>centroid_group 3</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>77178</v>
+        <v>43849</v>
+      </c>
+      <c r="E20" t="n">
+        <v>13</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.929166666666667</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.3413940256045519</v>
       </c>
     </row>
     <row r="21">
@@ -1689,14 +1460,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>group 19</t>
+          <t>centroid_group 4</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>14959</v>
+        <v>9482</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.08130081300813008</v>
       </c>
     </row>
     <row r="22">
@@ -1705,14 +1485,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>group 20</t>
+          <t>centroid_group 5</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>239637</v>
+        <v>33775</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.07042253521126761</v>
       </c>
     </row>
     <row r="23">
@@ -1721,14 +1510,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>group 21</t>
+          <t>centroid_group 6</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>12434</v>
+        <v>42171</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.3076923076923077</v>
       </c>
     </row>
     <row r="24">
@@ -1737,14 +1535,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>group 22</t>
+          <t>centroid_group 7</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>48188</v>
+        <v>10620</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.08368200836820085</v>
       </c>
     </row>
     <row r="25">
@@ -1753,14 +1560,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>group 23</t>
+          <t>resting row 0</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>58765</v>
+        <v>7721</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>60</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="26">
@@ -1769,14 +1585,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>group 24</t>
+          <t>resting row 1</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>85397</v>
+        <v>4968</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>60</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="27">
@@ -1785,14 +1610,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>group 25</t>
+          <t>resting row 2</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>133108</v>
+        <v>5624</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>60</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="28">
@@ -1801,14 +1635,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>group 26</t>
+          <t>resting row 3</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>7054</v>
+        <v>114239</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>60</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="29">
@@ -1817,14 +1660,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>group 27</t>
+          <t>resting row 4</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>24060</v>
+        <v>16994</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>60</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="30">
@@ -1833,14 +1685,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>group 28</t>
+          <t>resting row 5</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>12357</v>
+        <v>4546</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>60</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="31">
@@ -1849,14 +1710,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>group 29</t>
+          <t>resting row 6</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>40272</v>
+        <v>114006</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>60</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="32">
@@ -1865,14 +1735,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>group 30</t>
+          <t>resting row 7</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>178208</v>
+        <v>5884</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>60</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="33">
@@ -1881,446 +1760,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>group 31</t>
+          <t>resting row 8</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>61249</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>group 32</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" t="n">
-        <v>36538</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>centroid_group 0</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>4</v>
-      </c>
-      <c r="D35" t="n">
-        <v>52174</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>centroid_group 1</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>19</v>
-      </c>
-      <c r="D36" t="n">
-        <v>24211</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>centroid_group 2</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>5</v>
-      </c>
-      <c r="D37" t="n">
-        <v>17653</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>centroid_group 3</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>3</v>
-      </c>
-      <c r="D38" t="n">
-        <v>9186</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>centroid_group 4</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="n">
-        <v>10494</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>centroid_group 5</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>2</v>
-      </c>
-      <c r="D40" t="n">
-        <v>9906</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>centroid_group 6</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>2</v>
-      </c>
-      <c r="D41" t="n">
-        <v>15849</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>centroid_group 7</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>6</v>
-      </c>
-      <c r="D42" t="n">
-        <v>33042</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>centroid_group 8</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>3</v>
-      </c>
-      <c r="D43" t="n">
-        <v>98507</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>centroid_group 9</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>2</v>
-      </c>
-      <c r="D44" t="n">
-        <v>18271</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>centroid_group 10</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>2</v>
-      </c>
-      <c r="D45" t="n">
-        <v>92432</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>centroid_group 11</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>2</v>
-      </c>
-      <c r="D46" t="n">
-        <v>38215</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>centroid_group 12</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>2</v>
-      </c>
-      <c r="D47" t="n">
-        <v>11637</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>centroid_group 13</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>2</v>
-      </c>
-      <c r="D48" t="n">
-        <v>51054</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>centroid_group 14</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>3</v>
-      </c>
-      <c r="D49" t="n">
-        <v>37041</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>centroid_group 15</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>3</v>
-      </c>
-      <c r="D50" t="n">
-        <v>58929</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>centroid_group 16</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>3</v>
-      </c>
-      <c r="D51" t="n">
-        <v>231848</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>centroid_group 17</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>3</v>
-      </c>
-      <c r="D52" t="n">
-        <v>110054</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>centroid_group 18</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>2</v>
-      </c>
-      <c r="D53" t="n">
-        <v>34531</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>resting row 0</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" t="n">
-        <v>4855</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>resting row 1</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" t="n">
-        <v>4156</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>resting row 2</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" t="n">
-        <v>4332</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>resting row 3</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" t="n">
-        <v>4214</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>resting row 4</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" t="n">
-        <v>4132</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>resting row 5</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" t="n">
-        <v>13061</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>resting row 6</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="n">
-        <v>4623</v>
+        <v>105277</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>60</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.01666666666666667</v>
       </c>
     </row>
   </sheetData>
